--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,102 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-03-31 06:00 ~ 2026-04-01 06:00
+1. 白宮：美軍已準備好反制伊朗任何攻擊
+2026/04/01 04:18
+https://www.cna.com.tw/news/aopl/202604010009.aspx
+2. 尼坦雅胡：以色列將持續粉碎伊朗恐怖政權
+2026/04/01 03:24
+https://www.cna.com.tw/news/aopl/202604010007.aspx
+3. 川普稱戰爭很快將結束 美撤出後荷莫茲海峽將自動開放
+2026/04/01 03:00
+https://www.cna.com.tw/news/aopl/202604010006.aspx
+4. 伊朗：擁有必要意志結束戰爭 尋求保證衝突不重演
+2026/04/01 02:28
+https://www.cna.com.tw/news/aopl/202604010005.aspx
+5. 伊朗革命衛隊：再有領袖遇刺 將攻擊輝達等美企
+2026/04/01 01:23
+https://www.cna.com.tw/news/aopl/202604010004.aspx
+6. 能源價格飆升 3月歐元區通膨率衝上2.5%創1年多新高
+2026/03/31 22:23
+https://www.cna.com.tw/news/aopl/202603310403.aspx
+7. 中東戰火延燒 伊朗施壓青年運動打擊紅海航運
+2026/03/31 12:57
+https://www.cna.com.tw/news/aopl/202603313002.aspx
+8. 歐盟外長會議基輔登場 重申援烏與追究俄國責任
+2026/03/31 21:33
+https://www.cna.com.tw/news/aopl/202603310385.aspx
+9. 菲律賓總統簽署行政命令 對南海逾百島礁重新命名
+2026/03/31 22:56
+https://www.cna.com.tw/news/aopl/202603310409.aspx
+10. 中國巴基斯坦提五點倡議 促中東立即停火儘速和談
+2026/03/31 23:58
+https://www.cna.com.tw/news/aopl/202603310415.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-03-31 06:00 ~ 2026-04-01 06:00
+1. 尼坦雅胡：以色列將持續戰鬥 矢言「粉碎伊朗恐怖政權」 | 鉅亨網 - 國際政經
+2026-04-01 05:50
+https://news.cnyes.com/news/id/6403503
+2. 伊朗揚言攻擊中東美企 美國務院：沙國境內美國公民就地避難 | 鉅亨網 - 國際政經
+2026-04-01 05:40
+https://news.cnyes.com/news/id/6403481
+3. 川普：對伊戰爭很快將結束 荷姆茲海峽將「自動開放」 | 鉅亨網 - 國際政經
+2026-04-01 05:30
+https://news.cnyes.com/news/id/6403498
+4. 紐時：美軍PrSM飛彈疑似首度投入實戰 伊朗體育館遭重創 釀21死數百傷 | 鉅亨網 - 國際政經
+2026-04-01 05:20
+https://news.cnyes.com/news/id/6403362
+5. 〈美股盤後〉伊朗總統鬆口「願結束戰爭」道瓊狂飆逾1100點 台積電ADR飛升近7% | 鉅亨網 - 國際政經
+2026-04-01 05:00
+https://news.cnyes.com/news/id/6403509
+6. 英法拒參戰 川普嗆歐洲盟友：美國不會再幫你們 「自己去打仗」 | 鉅亨網 - 國際政經
+2026-04-01 04:30
+https://news.cnyes.com/news/id/6403390
+7. 川普籲盟友「奪回」荷姆茲海峽 能源供應風險升溫 | 鉅亨網 - 國際政經
+2026-04-01 03:00
+https://news.cnyes.com/news/id/6403337
+8. 美伊戰火續升溫！伊朗威脅攻擊蘋果、谷歌與微軟等美企 美防長籲德黑蘭達協議 | 鉅亨網 - 國際政經
+2026-04-01 00:10
+https://news.cnyes.com/news/id/6403348
+9. 伊朗戰爭推升能源成本 歐元區3月通膨寫2022年以來新高 | 鉅亨網 - 國際政經
+2026-03-31 19:20
+https://news.cnyes.com/news/id/6402979
+10. 荷姆茲海峽航運受阻 11國發聯合聲明 | 鉅亨網 - 國際政經
+2026-03-31 21:47
+https://news.cnyes.com/news/id/6403258</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,6 +625,102 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260402</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-04-01 06:00 ~ 2026-04-02 06:00
+1. 川普威脅退出北約 共和黨大老麥康奈跨黨派聯手反對
+2026/04/02 05:59
+https://www.cna.com.tw/news/aopl/202604020013.aspx
+2. 伊朗報復美企第一槍？亞馬遜巴林雲端設施傳遇襲起火
+2026/04/02 02:57
+https://www.cna.com.tw/news/aopl/202604020007.aspx
+3. 美伊正討論協議 以停火換取重啟荷莫茲海峽
+2026/04/02 02:34
+https://www.cna.com.tw/news/aopl/202604020006.aspx
+4. 范斯代川普下通牒：對伊朗失耐心 滿足美要求才停火
+2026/04/02 01:21
+https://www.cna.com.tw/news/aopl/202604020004.aspx
+5. 川普：美國很快會從伊朗戰事抽身 必要時將回頭打擊
+2026/04/01 22:28
+https://www.cna.com.tw/news/aopl/202604010386.aspx
+6. 川普指伊朗總統尋求停火 德黑蘭稱荷莫茲不對敵人開放
+2026/04/01 22:24
+https://www.cna.com.tw/news/aopl/202604010385.aspx
+7. 白宮：川普4/2將就伊朗戰事發表全國演說
+2026/04/01 12:03
+https://www.cna.com.tw/news/aopl/202604010106.aspx
+8. 教宗籲川普尋求停戰 盼復活節前結束中東衝突
+2026/04/01 13:33
+https://www.cna.com.tw/news/aopl/202604010142.aspx
+9. 歐盟援助烏克蘭 動用俄凍結資產利息520億元
+2026/04/01 22:31
+https://www.cna.com.tw/news/aopl/202604010387.aspx
+10. 俄稱全面掌控烏東盧甘斯克州 基輔駁戰場半年來沒變化
+2026/04/01 21:13
+https://www.cna.com.tw/news/aopl/202604010373.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260402</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-04-01 06:00 ~ 2026-04-02 06:00
+1. 伊朗否認停火說法 打臉川普稱「毫無根據」 | 鉅亨網 - 國際政經
+2026-04-02 01:00
+https://news.cnyes.com/news/id/6404962
+2. 伊朗外長：荷姆茲海峽的未來安排 將完全由伊朗與阿曼共同決定 | 鉅亨網 - 國際政經
+2026-04-02 00:10
+https://news.cnyes.com/news/id/6405015
+3. 來硬的！UAE擬聯手美國 武力重開荷姆茲海峽 全球油市震盪 | 鉅亨網 - 國際政經
+2026-04-02 05:20
+https://news.cnyes.com/news/id/6405038
+4. 伊朗、真主黨、胡塞 再次聯合襲擊以色列 | 鉅亨網 - 國際政經
+2026-04-01 20:33
+https://news.cnyes.com/news/id/6404828
+5. 運價飛天！亞洲國家瘋狂搶租美國油輪 日租金破30萬美元創史高 運費暴衝五倍 | 鉅亨網 - 國際政經
+2026-04-02 02:50
+https://news.cnyes.com/news/id/6405013
+6. 能源供應持續緊張！韓上調資源安全危機至三級 公家機關車輛改「單雙號限行」 | 鉅亨網 - 國際政經
+2026-04-02 05:40
+https://news.cnyes.com/news/id/6404935
+7. 亞洲搶買俄油補戰爭缺口！菲律賓睽違6年首進口、南韓加入搶購行列 | 鉅亨網 - 國際政經
+2026-04-02 04:00
+https://news.cnyes.com/news/id/6403581
+8. 不容外部勢力介入！伊朗外長：荷姆茲海峽的未來安排 將完全由伊朗與阿曼共同決定 | 鉅亨網 - 國際政經
+2026-04-02 00:10
+https://news.cnyes.com/news/id/6405015
+9. 資金大撤退！印度與台灣ETF創紀錄流出 市場情緒急轉 | 鉅亨網 - 美股雷達
+2026-04-02 02:00
+https://news.cnyes.com/news/id/6405039
+10. 伊朗總統發表致美國民眾公開信：提美伊關係被誤解、並無敵意、非主動發動戰爭 | 鉅亨網 - 美股雷達
+2026-04-02 05:55
+https://news.cnyes.com/news/id/6405109</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,102 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260402</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-04-01 06:00 ~ 2026-04-02 06:00
+1. 川普威脅退出北約 共和黨大老麥康奈跨黨派聯手反對
+2026/04/02 05:59
+https://www.cna.com.tw/news/aopl/202604020013.aspx
+2. 伊朗戰爭支持率狂瀉48百分點 傳統共和黨人轉向反戰
+2026/04/02 05:44
+https://www.cna.com.tw/news/aopl/202604020012.aspx
+3. 伊朗總統致信美國民眾 質疑川普師出無名
+2026/04/02 04:17
+https://www.cna.com.tw/news/aopl/202604020009.aspx
+4. 美伊正討論協議 以停火換取重啟荷莫茲海峽
+2026/04/02 02:34
+https://www.cna.com.tw/news/aopl/202604020006.aspx
+5. 范斯代川普下通牒：對伊朗失耐心 滿足美要求才停火
+2026/04/02 01:21
+https://www.cna.com.tw/news/aopl/202604020004.aspx
+6. 川普：美國很快會從伊朗戰事抽身 必要時將回頭打擊
+2026/04/01 22:28
+https://www.cna.com.tw/news/aopl/202604010386.aspx
+7. 川普指伊朗總統尋求停火 德黑蘭稱荷莫茲不對敵人開放
+2026/04/01 22:24
+https://www.cna.com.tw/news/aopl/202604010385.aspx
+8. 伊朗報復美企第一槍？亞馬遜巴林雲端設施傳遇襲起火
+2026/04/02 02:57
+https://www.cna.com.tw/news/aopl/202604020007.aspx
+9. 歐盟援助烏克蘭 動用俄凍結資產利息520億元
+2026/04/01 22:31
+https://www.cna.com.tw/news/aopl/202604010387.aspx
+10. 俄稱全面掌控烏東盧甘斯克州 基輔駁戰場半年來沒變化
+2026/04/01 21:13
+https://www.cna.com.tw/news/aopl/202604010373.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260402</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-04-01 06:00 ~ 2026-04-02 06:00
+1. 能源供應持續緊張！韓上調資源安全危機至三級 公家機關車輛改「單雙號限行」
+2026-04-02 05:40
+https://news.cnyes.com/news/id/6404935
+2. 來硬的！UAE擬聯手美國 武力重開荷姆茲海峽 全球油市震盪
+2026-04-02 05:20
+https://news.cnyes.com/news/id/6405038
+3. 伊朗否認停火說法 打臉川普稱「毫無根據」
+2026-04-02 01:00
+https://news.cnyes.com/news/id/6404962
+4. 不容外部勢力介入！伊朗外長：荷姆茲海峽的未來安排 將完全由伊朗與阿曼共同決定
+2026-04-02 00:10
+https://news.cnyes.com/news/id/6405015
+5. 伊朗、真主黨、胡塞 再次聯合襲擊以色列
+2026-04-01 20:33
+https://news.cnyes.com/news/id/6404828
+6. 川普稱伊朗提出停火 荷姆茲海峽未開放前不考慮
+2026-04-01 21:03
+https://news.cnyes.com/news/id/6404850
+7. 川普稱考慮退出NATO 不滿盟友未挺伊朗軍事行動
+2026-04-01 20:57
+https://news.cnyes.com/news/id/6404844
+8. 運價飛天！亞洲國家瘋狂搶租美國油輪 日租金破30萬美元創史高 運費暴衝五倍
+2026-04-02 02:50
+https://news.cnyes.com/news/id/6405013
+9. 亞洲搶買俄油補戰爭缺口！菲律賓睽違6年首進口、南韓加入搶購行列
+2026-04-02 04:00
+https://news.cnyes.com/news/id/6403581
+10. 伊朗外溢至美妝供應鏈，包材、運輸成本齊揚，業者示警終端售價恐上修
+2026-04-01 19:00
+https://news.cnyes.com/news/id/6404730</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +817,102 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260403</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-04-02 06:00 ~ 2026-04-03 06:00
+1. 英召集約40國談荷莫茲危機 要求立即無條件重開海峽
+2026/04/03 03:34
+https://www.cna.com.tw/news/aopl/202604030005.aspx
+2. 伊朗擬對通過荷莫茲海峽船舶收費 與阿曼起草通行協議
+2026/04/03 02:20
+https://www.cna.com.tw/news/aopl/202604033001.aspx
+3. 不滿艾普斯坦案處置方式 川普撤換美司法部長邦迪
+2026/04/03 02:37
+https://www.cna.com.tw/news/aopl/202604030004.aspx
+4. 遭到美、以數波攻擊 伊朗兩大鋼鐵廠被迫停擺
+2026/04/02 21:55
+https://www.cna.com.tw/news/aopl/202604020362.aspx
+5. 川普祭新藥品關稅、重整金屬稅 強推製造業回流美國
+2026/04/03 04:49
+https://www.cna.com.tw/news/aopl/202604030007.aspx
+6. 川普揚言將伊打回石器時代 德黑蘭威脅毀滅性攻擊美以
+2026/04/02 15:15
+https://www.cna.com.tw/news/aopl/202604020190.aspx
+7. 川普：未來2到3週將給伊朗最重擊 未達成協議將打擊供電網[影]
+2026/04/02 09:29
+https://www.cna.com.tw/news/aopl/202604023002.aspx
+8. 外長通話 伊朗承諾菲律賓籍油輪安全通行
+2026/04/02 19:00
+https://www.cna.com.tw/news/aopl/202604020302.aspx
+9. 美支持巴拿馬抗中扣押船舶 盧比歐批北京損害法治
+2026/04/03 01:04
+https://www.cna.com.tw/news/aopl/202604030003.aspx
+10. 能源危機加劇 孟加拉桶裝瓦斯漲價29%
+2026/04/02 20:22
+https://www.cna.com.tw/news/aopl/202604020338.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260403</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-04-02 06:00 ~ 2026-04-03 06:00
+1. 川普政府公告對鋼鐵、鋁、銅衍生品徵25%關稅 | 鉅亨網 - 美股雷達
+2026-04-03 04:59
+https://news.cnyes.com/news/id/6406580
+2. 川普政府擬對進口藥品課徵最高100%關稅 | 鉅亨網 - 國際政經
+2026-04-02 23:27
+https://news.cnyes.com/news/id/6406492
+3. 烏克蘭無人機狂襲 俄油港儲油設施損失四成 | 鉅亨網 - 國際政經
+2026-04-02 22:31
+https://news.cnyes.com/news/id/6406445
+4. 美上周初領失業金人數降至近兩年低點 就業市場陷「低招募、低裁員」 | 鉅亨網 - 美股雷達
+2026-04-02 22:00
+https://news.cnyes.com/news/id/6406268
+5. 國際油價暴衝10%！川普對伊朗強硬發言 點燃市場避險情緒 | 鉅亨網 - 能源
+2026-04-02 21:00
+https://news.cnyes.com/news/id/6406380
+6. 川普揚言持續打擊伊朗全球股市重挫、油價衝破100美元 | 鉅亨網 - 國際政經
+2026-04-02 15:31
+https://news.cnyes.com/news/id/6405907
+7. 伊朗傳尋求中國安全擔保 北京呼籲美以停止軍事行動 | 鉅亨網 - 國際政經
+2026-04-02 18:50
+https://news.cnyes.com/news/id/6406189
+8. 荷姆茲海峽有望恢復通行？伊朗與阿曼研擬監控機制 | 鉅亨網 - 國際政經
+2026-04-02 23:10
+https://news.cnyes.com/news/id/6406486
+9. 高盛：全球避險基金3月回檔幅度創四年多之最 亞洲避險基金暴跌7.3%最慘 | 鉅亨網 - 國際政經
+2026-04-02 11:40
+https://news.cnyes.com/news/id/6405209
+10. 最強救火隊集結！IEA、IMF、世銀發聯合聲明 將協調因應伊朗戰爭衝擊 | 鉅亨網 - 國際政經
+2026-04-02 11:21
+https://news.cnyes.com/news/id/6405459</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,6 +913,102 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260403</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-04-02 06:00 ~ 2026-04-03 06:00
+1. 英召集約40國談荷莫茲危機 要求立即無條件重開海峽
+2026/04/03 03:34
+https://www.cna.com.tw/news/aopl/202604030005.aspx
+2. 伊朗擬對通過荷莫茲海峽船舶收費 與阿曼起草通行協議
+2026/04/03 02:20
+https://www.cna.com.tw/news/aopl/202604033001.aspx
+3. 川普祭新藥品關稅、重整金屬稅 強推製造業回流美國
+2026/04/03 04:49
+https://www.cna.com.tw/news/aopl/202604030007.aspx
+4. 遭到美、以數波攻擊 伊朗兩大鋼鐵廠被迫停擺
+2026/04/02 21:55
+https://www.cna.com.tw/news/aopl/202604020362.aspx
+5. 川普揚言將伊打回石器時代 德黑蘭威脅毀滅性攻擊美以
+2026/04/02 15:15
+https://www.cna.com.tw/news/aopl/202604020190.aspx
+6. 美駐巴格達大使館警告 親伊朗團體2天內恐發動攻擊
+2026/04/02 16:36
+https://www.cna.com.tw/news/aopl/202604020228.aspx
+7. 烏克蘭無人機3度墜芬蘭 第3架距俄邊境僅1公里
+2026/04/02 19:33
+https://www.cna.com.tw/news/aopl/202604020319.aspx
+8. 能源危機加劇 孟加拉桶裝瓦斯漲價29%
+2026/04/02 20:22
+https://www.cna.com.tw/news/aopl/202604020338.aspx
+9. 中東危機影響 印度航空公司調升燃油費、機票漲價
+2026/04/02 16:28
+https://www.cna.com.tw/news/aopl/202604020225.aspx
+10. 美支持巴拿馬抗中扣押船舶 盧比歐批北京損害法治
+2026/04/03 01:04
+https://www.cna.com.tw/news/aopl/202604030003.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260403</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-04-02 06:00 ~ 2026-04-03 06:00
+1. 國際油價暴衝10%！川普對伊朗強硬發言 點燃市場避險情緒 | 鉅亨網 - 能源
+2026-04-02 21:00
+https://news.cnyes.com/news/id/6406380
+2. 烏克蘭無人機狂襲 俄油港儲油設施損失四成 | 鉅亨網 - 國際政經
+2026-04-02 22:31
+https://news.cnyes.com/news/id/6406445
+3. 川普政府擬對進口藥品課徵最高100%關稅 | 鉅亨網 - 國際政經
+2026-04-02 23:27
+https://news.cnyes.com/news/id/6406492
+4. 伊朗傳尋求中國安全擔保 北京呼籲美以停止軍事行動 | 鉅亨網 - 國際政經
+2026-04-02 18:50
+https://news.cnyes.com/news/id/6406189
+5. 伊朗最高領袖：繼續封鎖荷姆茲海峽 研究開闢潛在戰線 | 鉅亨網 - 國際政經
+2026-04-02 10:48
+https://news.cnyes.com/news/id/6405367
+6. 回應川普演說 伊朗：絕不容忍戰爭、談判、停火的「惡性循環」 | 鉅亨網 - 國際政經
+2026-04-02 16:40
+https://news.cnyes.com/news/id/6405997
+7. 荷姆茲海峽有望恢復通行？伊朗與阿曼研擬監控機制 | 鉅亨網 - 國際政經
+2026-04-02 23:10
+https://news.cnyes.com/news/id/6406486
+8. 烏克蘭無人機打擊 俄羅斯石油出口受阻 減產壓力迫在眉睫 | 鉅亨網 - 能源
+2026-04-02 19:20
+https://news.cnyes.com/news/id/6406271
+9. 最強救火隊集結！IEA、IMF、世銀發聯合聲明 將協調因應伊朗戰爭衝擊 | 鉅亨網 - 國際政經
+2026-04-02 11:21
+https://news.cnyes.com/news/id/6405459
+10. 高盛：全球避險基金3月回檔幅度創四年多之最 亞洲避險基金暴跌7.3%最慘 | 鉅亨網 - 國際政經
+2026-04-02 11:40
+https://news.cnyes.com/news/id/6405209</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,102 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260404</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-04-03 06:00 ~ 2026-04-04 06:00
+1. 傳美軍A-10墜毀飛行員獲救 伊朗擊落F-15一獲救一失聯
+2026/04/04 05:45
+https://www.cna.com.tw/news/aopl/202604040006.aspx
+2. 以色列空襲貝魯特 美警告伊朗恐攻擊黎巴嫩大學院校
+2026/04/04 04:04
+https://www.cna.com.tw/news/aopl/202604040005.aspx
+3. 川普接獲美軍戰機被擊落簡報 搜尋失聯人員仍在進行
+2026/04/04 02:47
+https://www.cna.com.tw/news/aopl/202604040003.aspx
+4. 傳美F-15E雙座戰機遭伊朗擊落 其中一名機員獲救
+2026/04/04 01:25
+https://www.cna.com.tw/news/aopl/202604040002.aspx
+5. 美國3月大增17.8萬名就業人口 失業率略降至4.3%
+2026/04/03 23:23
+https://www.cna.com.tw/news/aopl/202604030246.aspx
+6. 伊朗醫療設施遭空襲 世衛示警：多處公衛體系受創
+2026/04/03 19:59
+https://www.cna.com.tw/news/aopl/202604030218.aspx
+7. 確保荷莫茲海峽通行安全 比利時願協助掃雷
+2026/04/03 19:11
+https://www.cna.com.tw/news/aopl/202604030210.aspx
+8. 柬埔寨國會通過首部打詐法 詐騙中心猖獗引國際壓力
+2026/04/03 20:38
+https://www.cna.com.tw/news/aopl/202604030225.aspx
+9. 3月聯合國糧價指數漲2.4% 穀物供應足緩和植物油漲價衝擊
+2026/04/03 20:12
+https://www.cna.com.tw/news/aopl/202604030222.aspx
+10. 伊朗戰爭持續 白宮提議2027年國防預算1.5兆美元
+2026/04/03 22:04
+https://www.cna.com.tw/news/aopl/202604030237.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260404</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-04-03 06:00 ~ 2026-04-04 06:00
+1. CNN曝衛星照！伊朗攻擊沙烏地美軍基地炸毀「薩德」雷達、E-3預警機 | 鉅亨網 - 國際政經
+2026-04-03 20:00
+https://news.cnyes.com/news/id/6406996
+2. 報美國炸橋之仇！伊朗媒體稱將反擊「這些」目標 | 鉅亨網 - 國際政經
+2026-04-03 21:20
+https://news.cnyes.com/news/id/6406855
+3. 荷姆茲海峽僵局恐難解？聯合國安理會週末表決護航令、中俄法反對、內部分歧大 | 鉅亨網 - 國際政經
+2026-04-03 18:20
+https://news.cnyes.com/news/id/6406821
+4. 伊朗戰爭以來首艘西歐船隻！法國貨櫃船成功通過荷姆茲海峽 | 鉅亨網 - 國際政經
+2026-04-03 17:40
+https://news.cnyes.com/news/id/6406891
+5. 美國白打了？情報：伊朗約半數導彈發射裝置、數千架無人機「完好無損」 | 鉅亨網 - 國際政經
+2026-04-03 17:10
+https://news.cnyes.com/news/id/6406840
+6. 美以伊開戰第34天戰況彙整：川普威脅加強打擊、葉門胡塞發動第四波導彈攻擊 | 鉅亨網 - 國際政經
+2026-04-03 15:00
+https://news.cnyes.com/news/id/6406822
+7. 摩根大通示警：荷姆茲海峽封鎖若延至5月 油價恐飆上150美元 | 鉅亨網 - 能源
+2026-04-03 13:00
+https://news.cnyes.com/news/id/6406635
+8. 布蘭特原油現貨飆141美元、創2008年來新高！與期貨逆價差達32美元 | 鉅亨網 - 能源
+2026-04-03 08:10
+https://news.cnyes.com/news/id/6406625
+9. 伊朗戰爭以來首艘西歐船隻！法國貨櫃船成功通過荷姆茲海峽 | 鉅亨網 - 國際政經
+2026-04-03 17:40
+https://news.cnyes.com/news/id/6406891
+10. 非農就業強勢反彈！3月新增17.8萬創近一年新高、Fed利率按兵不動機率99.5% | 鉅亨網 - 國際政經
+2026-04-03 20:57
+https://news.cnyes.com/news/id/6406971</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,6 +1105,102 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260405</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-04-04 06:00 ~ 2026-04-05 06:00
+1. 以色列襲伊朗石化廠 尼坦雅胡：持續打擊德黑蘭政權
+2026/04/05 04:37
+https://www.cna.com.tw/news/aopl/202604050005.aspx
+2. 川普下達48小時通牒 伊朗若不讓步「地獄將降臨」
+2026/04/04 22:59
+https://www.cna.com.tw/news/aopl/202604040216.aspx
+3. 俄企自伊朗布什爾核電廠再撤198人 1員工死於彈片
+2026/04/04 23:10
+https://www.cna.com.tw/news/aopl/202604040217.aspx
+4. 伊朗多地遇襲 美以轟核電廠、水泥廠與石化中心
+2026/04/04 19:43
+https://www.cna.com.tw/news/aopl/202604040199.aspx
+5. 中東戰爭進入35天 美國已損失7架載人軍機
+2026/04/04 19:57
+https://www.cna.com.tw/news/aopl/202604040201.aspx
+6. 俄羅斯無人機攻擊烏克蘭東部市場 導致5死19傷
+2026/04/04 19:23
+https://www.cna.com.tw/news/aopl/202604040195.aspx
+7. 澤倫斯基抵達土耳其 將與艾爾段商討安全議題
+2026/04/04 21:04
+https://www.cna.com.tw/news/aopl/202604040209.aspx
+8. 艾爾段會晤澤倫斯基 商討能源航運安全與終結戰爭
+2026/04/05 05:44
+https://www.cna.com.tw/news/aopl/202604050007.aspx
+9. 阿富汗5.8強震增至12死4傷 含1家8人罹難
+2026/04/04 21:38
+https://www.cna.com.tw/news/aopl/202604040212.aspx
+10. 安理會延後表決荷莫茲海峽決議 中國反對授權動武
+2026/04/04 08:45
+https://www.cna.com.tw/news/aopl/202604040015.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260405</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-04-04 06:00 ~ 2026-04-05 06:00
+1. 川普再對伊朗下48小時最後通牒！伊朗強硬回應 | 鉅亨網 - 國際政經
+2026-04-04 23:11
+https://news.cnyes.com/news/id/6407446
+2. 美國兩架戰機遭伊朗擊落！美軍F-15E與A-10戰機受損、搜救行動持續 | 鉅亨網 - 國際政經
+2026-04-04 16:00
+https://news.cnyes.com/news/id/6407263
+3. 美國大使館遭襲內幕曝！損害遠超公開預期、伊朗打擊能力強 | 鉅亨網 - 國際政經
+2026-04-04 19:00
+https://news.cnyes.com/news/id/6407345
+4. 美軍展開搜救 飛行員被伊朗軍方俘虜？ | 鉅亨網 - 國際政經
+2026-04-04 10:00
+https://news.cnyes.com/news/id/6407083
+5. 美以伊開戰第35天戰況彙整：伊朗拒絕美國48小時停火建議、擊落美軍戰機 | 鉅亨網 - 國際政經
+2026-04-04 14:00
+https://news.cnyes.com/news/id/6407258
+6. 限制晶片設備出口中國！美國擬立新法 ASML舊款DUV恐也賣不了 | 鉅亨網 - 國際政經
+2026-04-04 12:10
+https://news.cnyes.com/news/id/6407108
+7. 川普推1.5兆美元國防預算創新高！削減教育、NASA與醫療支出引爭議 | 鉅亨網 - 國際政經
+2026-04-04 18:10
+https://news.cnyes.com/news/id/6407331
+8. 伊朗首次擊落美國戰機！美軍展開搜救 飛行員被伊朗軍方俘虜？ | 鉅亨網 - 國際政經
+2026-04-04 10:00
+https://news.cnyes.com/news/id/6407083
+9. 川普稱要再打伊朗「三週」引美軍官擔憂 撤軍怕丟臉、繼續恐難以抽身 | 鉅亨網 - 國際政經
+2026-04-04 11:10
+https://news.cnyes.com/news/id/6407104
+10. 川普「解放日」關稅滿一週年！美國企業與消費者仍受政策不確定性影響 | 鉅亨網 - 國際政經
+2026-04-04 09:00
+https://news.cnyes.com/news/id/6406778</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/news_push_data/telegram/message.xlsx
+++ b/news_push_data/telegram/message.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1201,6 +1201,102 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260406</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>中央社</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>中央社 Top10
+區間：2026-04-03 06:00 ~ 2026-04-06 06:00
+1. 開放荷莫茲海峽最後通牒 川普暗示美東4/7晚間8時
+2026/04/06 02:24
+https://www.cna.com.tw/news/aopl/202604060003.aspx
+2. 遭烏攻擊中斷運作 傳俄波羅的海港口恢復原油裝載
+2026/04/06 05:22
+https://www.cna.com.tw/news/aopl/202604060007.aspx
+3. 油輪載伊拉克原油通過荷莫茲海峽 將在馬來西亞卸貨
+2026/04/06 04:45
+https://www.cna.com.tw/news/aopl/202604060006.aspx
+4. OPEC+：受損能源設施修復費時且昂貴
+2026/04/06 02:52
+https://www.cna.com.tw/news/aopl/202604060004.aspx
+5. 伊朗持續空襲鄰國 阿聯：準備好加入美國為首行動
+2026/04/06 00:45
+https://www.cna.com.tw/news/aopl/202604060002.aspx
+6. 德州油罐車撞電線起火 司機燒傷情況危急
+2026/04/06 05:51
+https://www.cna.com.tw/news/aopl/202604060008.aspx
+7. 伊朗局部解封荷莫茲海峽 允許基本物資船隻通行
+2026/04/05 16:50
+https://www.cna.com.tw/news/aopl/202604050127.aspx
+8. 美軍成功營救F-15E飛官 川普將召開記者會說明
+2026/04/05 22:40
+https://www.cna.com.tw/news/aopl/202604050193.aspx
+9. 川普重申開放海峽 揚言4/7打擊伊朗發電廠與橋梁
+2026/04/05 22:09
+https://www.cna.com.tw/news/aopl/202604050190.aspx
+10. 美國3月大增17.8萬名就業人口 失業率略降至4.3%
+2026/04/03 23:23
+https://www.cna.com.tw/news/aopl/202604030246.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260406</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>鉅亨網</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>鉅亨網 Top10
+區間：2026-04-03 06:00 ~ 2026-04-06 06:00
+1. 美軍機救援飛行員又遭擊落？伊朗宣稱擊中C-130、兩架「黑鷹」
+2026-04-05 18:09
+https://news.cnyes.com/news/id/6407657
+2. 美軍遭伊朗擊落F-15E失蹤機組員獲救！川普發文：美國歷史上最大膽的搜救行動之一
+2026-04-05 12:30
+https://news.cnyes.com/news/id/6407576
+3. 科威特石油總部遭無人機轟炸起火！伊朗擴大攻擊能源設施
+2026-04-05 11:00
+https://news.cnyes.com/news/id/6407546
+4. 伊朗批准人道物資船通行荷姆茲海峽！擬推收費與分級制度
+2026-04-05 16:00
+https://news.cnyes.com/news/id/6407612
+5. 川普再對伊朗下48小時最後通牒！伊朗強硬回應
+2026-04-04 23:11
+https://news.cnyes.com/news/id/6407446
+6. 川普再次放話：4/7將是伊朗發電廠日、大橋日
+2026-04-05 20:58
+https://news.cnyes.com/news/id/6407714
+7. 本週操盤筆記：美國3月CPI、Fed會議紀錄
+2026-04-05 21:50
+https://news.cnyes.com/news/id/6406533
+8. 非農就業強勢反彈！3月新增17.8萬創近一年新高、Fed利率按兵不動機率99.5%
+2026-04-03 20:57
+https://news.cnyes.com/news/id/6406971
+9. 伊朗戰爭演變成「亞洲危機」 面臨「三大挑戰」
+2026-04-05 21:00
+https://news.cnyes.com/news/id/6407551
+10. 全球原油庫存「這時」將見底！摩根大通算出「停擺時間表」
+2026-04-05 10:20
+https://news.cnyes.com/news/id/6407460</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
